--- a/data/trans_dic/P1403-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1403-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>43,04%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,43; 28,9</t>
+          <t>23,4; 28,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,92; 38,3</t>
+          <t>32,02; 38,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,51; 34,03</t>
+          <t>27,27; 33,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32,36; 39,78</t>
+          <t>31,53; 39,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30,92; 36,1</t>
+          <t>30,97; 36,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,62; 45,34</t>
+          <t>39,25; 45,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,86; 41,32</t>
+          <t>35,15; 41,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>46,99; 52,63</t>
+          <t>45,98; 51,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28,38; 32,33</t>
+          <t>28,52; 32,35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37,32; 41,68</t>
+          <t>37,22; 41,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,37; 37,17</t>
+          <t>32,58; 37,24</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>42,03; 46,76</t>
+          <t>40,74; 45,1</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>14,67%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,94; 8,27</t>
+          <t>5,81; 8,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,34; 11,08</t>
+          <t>8,46; 11,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,6; 12,39</t>
+          <t>9,49; 12,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,22; 16,48</t>
+          <t>14,26; 17,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,32; 7,73</t>
+          <t>5,37; 7,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,93; 9,73</t>
+          <t>6,99; 9,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,48; 12,5</t>
+          <t>9,5; 12,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,51; 41,56</t>
+          <t>12,46; 14,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,92; 7,67</t>
+          <t>5,91; 7,65</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,09; 9,94</t>
+          <t>8,07; 10,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,91; 11,92</t>
+          <t>9,8; 11,92</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,99; 31,12</t>
+          <t>13,69; 15,63</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,37%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,03; 9,6</t>
+          <t>5,15; 9,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,33; 12,0</t>
+          <t>6,55; 12,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,82; 13,28</t>
+          <t>7,78; 13,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,57; 20,15</t>
+          <t>14,76; 20,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,94; 8,23</t>
+          <t>3,99; 8,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,55; 9,88</t>
+          <t>4,54; 9,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 8,3</t>
+          <t>3,67; 8,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,58; 13,3</t>
+          <t>9,84; 13,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,0; 8,21</t>
+          <t>5,11; 8,17</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,25; 10,4</t>
+          <t>6,04; 10,07</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,37; 10,11</t>
+          <t>6,43; 10,06</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,43; 15,69</t>
+          <t>12,88; 16,13</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>20,08%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,96; 14,33</t>
+          <t>11,93; 14,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,48; 18,19</t>
+          <t>15,47; 18,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,06; 16,64</t>
+          <t>13,9; 16,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,03; 19,84</t>
+          <t>17,73; 20,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,77; 18,24</t>
+          <t>15,79; 18,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,47; 22,36</t>
+          <t>19,72; 22,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,38; 19,15</t>
+          <t>16,46; 19,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,28; 40,39</t>
+          <t>19,81; 21,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,25; 15,91</t>
+          <t>14,04; 15,83</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,02; 19,85</t>
+          <t>18,03; 19,93</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,58; 17,37</t>
+          <t>15,59; 17,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,49; 29,54</t>
+          <t>19,3; 20,94</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>185268</t>
+          <t>202054</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>375862</t>
+          <t>399259</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>561130</t>
+          <t>601313</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>241782; 298172</t>
+          <t>241450; 298561</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311092; 373327</t>
+          <t>312069; 371636</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>207551; 256707</t>
+          <t>205692; 255055</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>166119; 204251</t>
+          <t>181934; 225147</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>406679; 474778</t>
+          <t>407253; 475912</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>529598; 606119</t>
+          <t>524615; 604742</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>346715; 411020</t>
+          <t>349592; 413020</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>353369; 395832</t>
+          <t>377121; 421573</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>665939; 758843</t>
+          <t>669288; 759263</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>862635; 963336</t>
+          <t>860281; 957454</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>566218; 650027</t>
+          <t>569789; 651389</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>531866; 591756</t>
+          <t>569246; 630171</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>324373</t>
+          <t>349775</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>469185</t>
+          <t>295123</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>793558</t>
+          <t>644898</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>100583; 140115</t>
+          <t>98416; 140111</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>163790; 217640</t>
+          <t>166241; 219860</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>199305; 257339</t>
+          <t>197003; 257104</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>233827; 377269</t>
+          <t>317733; 381978</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>84449; 122716</t>
+          <t>85271; 124826</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>121670; 170806</t>
+          <t>122666; 170538</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>188429; 248610</t>
+          <t>188869; 248706</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>279689; 928864</t>
+          <t>270242; 321280</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>194334; 251748</t>
+          <t>193916; 251162</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>300721; 369702</t>
+          <t>300088; 372405</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>402763; 484674</t>
+          <t>398369; 484628</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>587517; 1407601</t>
+          <t>601746; 687348</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>110875</t>
+          <t>121996</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>73746</t>
+          <t>85395</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>184620</t>
+          <t>207391</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>27730; 52935</t>
+          <t>28398; 54019</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30435; 57745</t>
+          <t>31526; 58971</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42779; 72631</t>
+          <t>42536; 72504</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>94027; 130073</t>
+          <t>104688; 143357</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18747; 39231</t>
+          <t>19008; 39762</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20880; 45317</t>
+          <t>20821; 45128</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20974; 45575</t>
+          <t>20142; 47229</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>63230; 87847</t>
+          <t>72231; 102107</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>51423; 84433</t>
+          <t>52494; 83944</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>58725; 97761</t>
+          <t>56737; 94682</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>69871; 110774</t>
+          <t>70448; 110277</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>162333; 204839</t>
+          <t>185856; 232785</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>620516</t>
+          <t>673824</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>918793</t>
+          <t>779777</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1539309</t>
+          <t>1453602</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>391893; 469366</t>
+          <t>390835; 467759</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>529237; 621894</t>
+          <t>529119; 626223</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>474778; 562110</t>
+          <t>469529; 555415</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>483570; 684182</t>
+          <t>623092; 715848</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>533039; 616523</t>
+          <t>533685; 618416</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>691301; 793759</t>
+          <t>700216; 798613</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>578552; 676329</t>
+          <t>581449; 679234</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>739539; 1473218</t>
+          <t>737624; 818769</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>948521; 1059189</t>
+          <t>934256; 1053357</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1256112; 1383366</t>
+          <t>1256861; 1389016</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1076526; 1200325</t>
+          <t>1076896; 1206419</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1311747; 2095643</t>
+          <t>1396797; 1515663</t>
         </is>
       </c>
     </row>
